--- a/artfynd/A 5755-2022 artfynd.xlsx
+++ b/artfynd/A 5755-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 5755-2022 artfynd.xlsx
+++ b/artfynd/A 5755-2022 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>74083741</v>
       </c>
       <c r="B2" t="n">
-        <v>101808</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104178</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549131.4296358089</v>
+        <v>549131</v>
       </c>
       <c r="R2" t="n">
-        <v>6252565.074026677</v>
+        <v>6252565</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1988-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1989-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">

--- a/artfynd/A 5755-2022 artfynd.xlsx
+++ b/artfynd/A 5755-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74083741</v>
       </c>
       <c r="B2" t="n">
-        <v>104178</v>
+        <v>104187</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 5755-2022 artfynd.xlsx
+++ b/artfynd/A 5755-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74083741</v>
       </c>
       <c r="B2" t="n">
-        <v>104187</v>
+        <v>104190</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 5755-2022 artfynd.xlsx
+++ b/artfynd/A 5755-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74083741</v>
       </c>
       <c r="B2" t="n">
-        <v>104190</v>
+        <v>104217</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 5755-2022 artfynd.xlsx
+++ b/artfynd/A 5755-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74083741</v>
       </c>
       <c r="B2" t="n">
-        <v>104217</v>
+        <v>104223</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 5755-2022 artfynd.xlsx
+++ b/artfynd/A 5755-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74083741</v>
       </c>
       <c r="B2" t="n">
-        <v>104223</v>
+        <v>104230</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 5755-2022 artfynd.xlsx
+++ b/artfynd/A 5755-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74083741</v>
       </c>
       <c r="B2" t="n">
-        <v>104230</v>
+        <v>104234</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 5755-2022 artfynd.xlsx
+++ b/artfynd/A 5755-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74083741</v>
       </c>
       <c r="B2" t="n">
-        <v>104234</v>
+        <v>104241</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 5755-2022 artfynd.xlsx
+++ b/artfynd/A 5755-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74083741</v>
       </c>
       <c r="B2" t="n">
-        <v>104244</v>
+        <v>104249</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 5755-2022 artfynd.xlsx
+++ b/artfynd/A 5755-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74083741</v>
       </c>
       <c r="B2" t="n">
-        <v>104249</v>
+        <v>104257</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 5755-2022 artfynd.xlsx
+++ b/artfynd/A 5755-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74083741</v>
       </c>
       <c r="B2" t="n">
-        <v>104257</v>
+        <v>104267</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 5755-2022 artfynd.xlsx
+++ b/artfynd/A 5755-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74083741</v>
       </c>
       <c r="B2" t="n">
-        <v>104267</v>
+        <v>104757</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
